--- a/docs/AIMS_Tiles_Columns.xlsx
+++ b/docs/AIMS_Tiles_Columns.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="32">
   <si>
     <t xml:space="preserve">PIT_ID</t>
   </si>
@@ -84,6 +84,21 @@
   </si>
   <si>
     <t xml:space="preserve">P20000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montipora aequituberculata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024Oct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T03</t>
   </si>
   <si>
     <t xml:space="preserve">NAME</t>
@@ -185,7 +200,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -208,6 +223,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -333,13 +352,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="23.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="16.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.81"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="1" width="11.53"/>
   </cols>
   <sheetData>
@@ -526,6 +545,57 @@
         <v>7</v>
       </c>
       <c r="E12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>45580</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -552,7 +622,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -562,7 +632,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -572,12 +642,12 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -587,12 +657,12 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/docs/AIMS_Tiles_Columns.xlsx
+++ b/docs/AIMS_Tiles_Columns.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="34">
   <si>
     <t xml:space="preserve">PIT_ID</t>
   </si>
@@ -99,6 +99,12 @@
   </si>
   <si>
     <t xml:space="preserve">T03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T02</t>
   </si>
   <si>
     <t xml:space="preserve">NAME</t>
@@ -352,7 +358,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
@@ -594,6 +600,40 @@
         <v>23</v>
       </c>
       <c r="E15" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="6" t="n">
         <v>45580</v>
       </c>
     </row>
@@ -622,7 +662,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -632,7 +672,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -642,12 +682,12 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -657,12 +697,12 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/docs/AIMS_Tiles_Columns.xlsx
+++ b/docs/AIMS_Tiles_Columns.xlsx
@@ -8,8 +8,9 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Tile" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Species" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Tile" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Species" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="79">
   <si>
     <t xml:space="preserve">PIT_ID</t>
   </si>
@@ -105,6 +106,141 @@
   </si>
   <si>
     <t xml:space="preserve">MIS5T02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIS5T47</t>
   </si>
   <si>
     <t xml:space="preserve">NAME</t>
@@ -247,125 +383,19 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E63"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="16.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.81"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13.82"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="6" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -634,6 +664,788 @@
         <v>23</v>
       </c>
       <c r="E17" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E52" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>45580</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>45595</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63" s="6" t="n">
         <v>45580</v>
       </c>
     </row>
@@ -649,20 +1461,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.21"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="2" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -672,7 +1484,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -682,12 +1494,12 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -697,12 +1509,12 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -714,4 +1526,165 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A2:C12"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="C2" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A2, ", MIS5T", B2)</f>
+        <v>0, MIS5T37</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <f aca="false">B2+1</f>
+        <v>38</v>
+      </c>
+      <c r="C3" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A3, ", MIS5T", B3)</f>
+        <v>1, MIS5T38</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <f aca="false">B3+1</f>
+        <v>39</v>
+      </c>
+      <c r="C4" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A4, ", MIS5T", B4)</f>
+        <v>2, MIS5T39</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="0" t="n">
+        <f aca="false">B4+1</f>
+        <v>40</v>
+      </c>
+      <c r="C5" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A5, ", MIS5T", B5)</f>
+        <v>3, MIS5T40</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="0" t="n">
+        <f aca="false">B5+1</f>
+        <v>41</v>
+      </c>
+      <c r="C6" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A6, ", MIS5T", B6)</f>
+        <v>4, MIS5T41</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="0" t="n">
+        <f aca="false">B6+1</f>
+        <v>42</v>
+      </c>
+      <c r="C7" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A7, ", MIS5T", B7)</f>
+        <v>5, MIS5T42</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <f aca="false">B7+1</f>
+        <v>43</v>
+      </c>
+      <c r="C8" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A8, ", MIS5T", B8)</f>
+        <v>6, MIS5T43</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="0" t="n">
+        <f aca="false">B8+1</f>
+        <v>44</v>
+      </c>
+      <c r="C9" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A9, ", MIS5T", B9)</f>
+        <v>7, MIS5T44</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="0" t="n">
+        <f aca="false">B9+1</f>
+        <v>45</v>
+      </c>
+      <c r="C10" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A10, ", MIS5T", B10)</f>
+        <v>8, MIS5T45</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="0" t="n">
+        <f aca="false">B10+1</f>
+        <v>46</v>
+      </c>
+      <c r="C11" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A11, ", MIS5T", B11)</f>
+        <v>9, MIS5T46</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="0" t="n">
+        <f aca="false">B11+1</f>
+        <v>47</v>
+      </c>
+      <c r="C12" s="0" t="str">
+        <f aca="false">_xlfn.CONCAT(A12, ", MIS5T", B12)</f>
+        <v>10, MIS5T47</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>